--- a/input/timetable/Управление персоналом.xlsx
+++ b/input/timetable/Управление персоналом.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>

--- a/input/timetable/Управление персоналом.xlsx
+++ b/input/timetable/Управление персоналом.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="135">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -122,13 +125,25 @@
     <t>Физическая культура и спорт (лек 8ч)</t>
   </si>
   <si>
+    <t>Гардт А.А.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Евсеенко Е.А.</t>
+  </si>
+  <si>
     <t>404-31</t>
+  </si>
+  <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
+    <t>Бутенко Н.А.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -136,6 +151,9 @@
 </t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Направление </t>
   </si>
   <si>
@@ -145,6 +163,18 @@
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Наумова А.А.</t>
+  </si>
+  <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
+    <t>Литовченко А.С.</t>
+  </si>
+  <si>
     <t>1-2.</t>
   </si>
   <si>
@@ -157,12 +187,21 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Забирова В.Х.</t>
+  </si>
+  <si>
+    <t>Плесовских И.Н.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф. сфере (24ч), п/г 1, К407</t>
   </si>
   <si>
     <t>Иностранный язык в проф. сфере (24ч), п/г 2, К407</t>
   </si>
   <si>
+    <t>Беленикина О.В.</t>
+  </si>
+  <si>
     <t>Управленческий учет и учет персонала (пр), К507</t>
   </si>
   <si>
@@ -181,6 +220,9 @@
     <t>Трудовой потенциал социально-экономических систем (пр), К504</t>
   </si>
   <si>
+    <t>Сметанина Г.А.</t>
+  </si>
+  <si>
     <t>"___"_______ 2026 г.</t>
   </si>
   <si>
@@ -205,9 +247,27 @@
     <t>Кадровая политика и управление трудовой деятельностью в организации                                                        ТО: 02.02.2026-01.04.2026</t>
   </si>
   <si>
+    <t>Ахтемзянова Н.М.</t>
+  </si>
+  <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Костюнина М.В.</t>
+  </si>
+  <si>
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Андриено А.И.</t>
+  </si>
+  <si>
+    <t>Ашарин А.А.</t>
+  </si>
+  <si>
+    <t>Имамвердиева М.И.</t>
+  </si>
+  <si>
     <t>День самостотятельной работы</t>
   </si>
   <si>
@@ -238,12 +298,21 @@
     <t xml:space="preserve">М.И. Имамвердиева </t>
   </si>
   <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык (пр), К412</t>
   </si>
   <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Лукиянчина Е.В.</t>
+  </si>
+  <si>
+    <t>Срыбник-Серебряный А.С.</t>
+  </si>
+  <si>
     <t>Экономика труда (пр), К506//</t>
   </si>
   <si>
@@ -274,6 +343,15 @@
     <t>// Работа в команде (пр), К506</t>
   </si>
   <si>
+    <t>Попова Е.В.</t>
+  </si>
+  <si>
+    <t>Исаева И.А.</t>
+  </si>
+  <si>
+    <t>Исаева И.А./Усаева Н.Р</t>
+  </si>
+  <si>
     <t>Основы социального страхования (лек)/(пр), К604</t>
   </si>
   <si>
@@ -295,6 +373,9 @@
     <t>//ФТД: Коммуникации в управленческой деятельности (пр), К506</t>
   </si>
   <si>
+    <t>Колесник А.А./Сергеева И.В.</t>
+  </si>
+  <si>
     <t>Стратегическое управление персоналом (пр)/(лек), К506/К504</t>
   </si>
   <si>
@@ -311,6 +392,9 @@
   </si>
   <si>
     <t>Иностранный язык в проф. сфере, п/г 2, К407</t>
+  </si>
+  <si>
+    <t>Колесник А.А.</t>
   </si>
   <si>
     <t>Трудовой потенциал социально-экономических систем (лек), К506</t>
@@ -464,7 +548,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +567,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -494,7 +584,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -611,6 +701,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -740,6 +843,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1108,6 +1224,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1143,6 +1268,17 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1220,7 +1356,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1264,28 +1400,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1306,10 +1445,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1324,27 +1463,27 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1352,7 +1491,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1362,27 +1501,27 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1391,525 +1530,597 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2232,7 +2443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2241,10 +2452,11 @@
     <col min="4" max="4" width="18.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2252,15 +2464,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2268,39 +2480,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2310,46 +2522,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="69" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" s="70" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>0</v>
@@ -2360,359 +2572,403 @@
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="G10" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="82"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="143" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="71"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>3</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="85"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="146"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="148"/>
+      <c r="G12" s="93"/>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>4</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
+      <c r="C13" s="146"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="148"/>
+      <c r="G13" s="72"/>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>5</v>
       </c>
-      <c r="C14" s="86"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="88"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32">
+      <c r="C14" s="149"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="73"/>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="33">
         <v>1</v>
       </c>
-      <c r="C15" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="82"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="143" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
         <v>2</v>
       </c>
-      <c r="C16" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="91"/>
-    </row>
-    <row r="17" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
+      <c r="C16" s="152" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="93" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
         <v>3</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="158" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="159"/>
+      <c r="E17" s="159"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17" s="63"/>
+    </row>
+    <row r="18" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="155"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="78"/>
+    </row>
+    <row r="19" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="33">
+        <v>2</v>
+      </c>
+      <c r="C19" s="161"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="86"/>
+    </row>
+    <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
+        <v>3</v>
+      </c>
+      <c r="C20" s="164"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="85"/>
+    </row>
+    <row r="21" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29">
+        <v>4</v>
+      </c>
+      <c r="C21" s="106" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="107"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="91" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29">
+        <v>5</v>
+      </c>
+      <c r="C22" s="140" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="91" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1</v>
+      </c>
+      <c r="C23" s="167"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="99"/>
+      <c r="G23" s="92" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
+        <v>2</v>
+      </c>
+      <c r="C24" s="109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29">
+        <v>3</v>
+      </c>
+      <c r="C25" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="36"/>
+      <c r="B26" s="31">
+        <v>4</v>
+      </c>
+      <c r="C26" s="112"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="84"/>
+    </row>
+    <row r="27" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33">
+        <v>1</v>
+      </c>
+      <c r="C27" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="29">
+        <v>2</v>
+      </c>
+      <c r="C28" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="37"/>
+      <c r="B29" s="29">
+        <v>3</v>
+      </c>
+      <c r="C29" s="115"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="91"/>
+    </row>
+    <row r="30" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="38"/>
+      <c r="B30" s="31">
+        <v>4</v>
+      </c>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="84"/>
+    </row>
+    <row r="31" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="97"/>
-      <c r="N17" s="62"/>
-    </row>
-    <row r="18" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="94"/>
-    </row>
-    <row r="19" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
-        <v>2</v>
-      </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
-    </row>
-    <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="B31" s="33">
+        <v>1</v>
+      </c>
+      <c r="C31" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="92" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29">
         <v>3</v>
       </c>
-      <c r="C20" s="101"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="103"/>
-    </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
+      <c r="C32" s="124"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="78"/>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="35">
         <v>4</v>
       </c>
-      <c r="C21" s="104" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="105"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103"/>
-    </row>
-    <row r="22" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28">
+      <c r="C33" s="133"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="91"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="41"/>
+      <c r="B34" s="31">
         <v>5</v>
       </c>
-      <c r="C22" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="76"/>
-    </row>
-    <row r="23" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
-        <v>1</v>
-      </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="127"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
-        <v>2</v>
-      </c>
-      <c r="C24" s="77" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="79"/>
-    </row>
-    <row r="25" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
-        <v>3</v>
-      </c>
-      <c r="C25" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79"/>
-    </row>
-    <row r="26" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="35"/>
-      <c r="B26" s="30">
-        <v>4</v>
-      </c>
-      <c r="C26" s="134"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="136"/>
-    </row>
-    <row r="27" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
-        <v>1</v>
-      </c>
-      <c r="C27" s="131" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="133"/>
-    </row>
-    <row r="28" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="28">
-        <v>2</v>
-      </c>
-      <c r="C28" s="104" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="111"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A29" s="36"/>
-      <c r="B29" s="28">
-        <v>3</v>
-      </c>
-      <c r="C29" s="137"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="139"/>
-    </row>
-    <row r="30" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="30">
-        <v>4</v>
-      </c>
-      <c r="C30" s="140"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="142"/>
-    </row>
-    <row r="31" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="32">
-        <v>1</v>
-      </c>
-      <c r="C31" s="128" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="129"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="130"/>
-    </row>
-    <row r="32" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="28">
-        <v>3</v>
-      </c>
-      <c r="C32" s="112"/>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="39"/>
-      <c r="B33" s="34">
-        <v>4</v>
-      </c>
-      <c r="C33" s="121"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="123"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="40"/>
-      <c r="B34" s="30">
-        <v>5</v>
-      </c>
-      <c r="C34" s="124"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="126"/>
-    </row>
-    <row r="35" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="43"/>
-      <c r="B36" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="115" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="116"/>
-      <c r="E36" s="116"/>
-      <c r="F36" s="117"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="44"/>
-      <c r="B37" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="104" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37" s="105"/>
-      <c r="E37" s="105"/>
-      <c r="F37" s="111"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="45"/>
-      <c r="B38" s="61" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="108" t="s">
+      <c r="C34" s="136"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="84"/>
+    </row>
+    <row r="35" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="130"/>
+      <c r="D35" s="131"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="77"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="44"/>
+      <c r="B36" s="60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="127" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="129"/>
+      <c r="G36" s="95" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="45"/>
+      <c r="B37" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="93" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="46"/>
+      <c r="B38" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="121" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="122"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="123"/>
+      <c r="G38" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="109"/>
-      <c r="E38" s="109"/>
-      <c r="F38" s="110"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C24:F24"/>
@@ -2729,6 +2985,21 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2766,7 +3037,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2774,11 +3045,11 @@
     <col min="3" max="3" width="21.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2786,15 +3057,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2802,39 +3073,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2844,402 +3115,446 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="69" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="167" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" s="70" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="193" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="49"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="146" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="147"/>
-      <c r="E10" s="147"/>
-      <c r="F10" s="148"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28">
+      <c r="C10" s="194" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="195"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="196"/>
+      <c r="G10" s="92" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>2</v>
       </c>
-      <c r="C11" s="89" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="91"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="152" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="91" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>3</v>
       </c>
-      <c r="C12" s="161" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="162"/>
-      <c r="E12" s="162"/>
-      <c r="F12" s="163"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="136"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="32">
+      <c r="C12" s="197" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="198"/>
+      <c r="E12" s="198"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="78"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="84"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="33">
         <v>1</v>
       </c>
-      <c r="C14" s="128" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="100" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="92" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29">
         <v>2</v>
       </c>
-      <c r="C15" s="161" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="162"/>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="197" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
         <v>3</v>
       </c>
-      <c r="C16" s="89" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="91"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="35"/>
-      <c r="B17" s="30">
+      <c r="C16" s="152" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="36"/>
+      <c r="B17" s="31">
         <v>4</v>
       </c>
-      <c r="C17" s="143"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="145"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="32">
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
+      <c r="E17" s="173"/>
+      <c r="F17" s="174"/>
+      <c r="G17" s="72"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="33">
         <v>1</v>
       </c>
-      <c r="C18" s="146"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="148"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28">
+      <c r="C18" s="194"/>
+      <c r="D18" s="195"/>
+      <c r="E18" s="195"/>
+      <c r="F18" s="196"/>
+      <c r="G18" s="95"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="164" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="166"/>
-    </row>
-    <row r="20" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="C19" s="184" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="185"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="186"/>
+      <c r="G19" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
         <v>3</v>
       </c>
-      <c r="C20" s="161" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="163"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="35"/>
-      <c r="B21" s="30">
+      <c r="C20" s="197" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="198"/>
+      <c r="E20" s="198"/>
+      <c r="F20" s="199"/>
+      <c r="G20" s="91" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="36"/>
+      <c r="B21" s="31">
         <v>4</v>
       </c>
-      <c r="C21" s="152" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="154"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="C21" s="203" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="204"/>
+      <c r="E21" s="204"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="87" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="33">
         <v>1</v>
       </c>
-      <c r="C22" s="155"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="157"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28">
+      <c r="C22" s="206"/>
+      <c r="D22" s="207"/>
+      <c r="E22" s="207"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="92"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29">
         <v>2</v>
       </c>
-      <c r="C23" s="121"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
+      <c r="C23" s="133"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="91"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
         <v>3</v>
       </c>
-      <c r="C24" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="91"/>
-    </row>
-    <row r="25" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="35"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="143"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="145"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32">
+      <c r="C24" s="152" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="72"/>
+    </row>
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="36"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="73"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="33">
         <v>1</v>
       </c>
-      <c r="C26" s="158"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="160"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="36"/>
-      <c r="B27" s="26">
+      <c r="C26" s="209"/>
+      <c r="D26" s="210"/>
+      <c r="E26" s="210"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="83"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="27">
         <v>2</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="123"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="28">
+      <c r="C27" s="133"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="78"/>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="29">
         <v>3</v>
       </c>
-      <c r="C28" s="181" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="182"/>
-      <c r="E28" s="182"/>
-      <c r="F28" s="183"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="37"/>
-      <c r="B29" s="30">
+      <c r="C28" s="187" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="188"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="189"/>
+      <c r="G28" s="91" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="31">
         <v>4</v>
       </c>
-      <c r="C29" s="175" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="176"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="177"/>
-    </row>
-    <row r="30" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="C29" s="178" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="179"/>
+      <c r="E29" s="179"/>
+      <c r="F29" s="180"/>
+      <c r="G29" s="87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="33">
         <v>2</v>
       </c>
-      <c r="C30" s="172" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="173"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="174"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="39"/>
-      <c r="B31" s="28">
+      <c r="C30" s="175" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="176"/>
+      <c r="E30" s="176"/>
+      <c r="F30" s="177"/>
+      <c r="G30" s="95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="29">
         <v>3</v>
       </c>
-      <c r="C31" s="164" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="166"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="28">
+      <c r="C31" s="184" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="93" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29">
         <v>4</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="123"/>
-    </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="30">
+      <c r="C32" s="133"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="72"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="41"/>
+      <c r="B33" s="31">
         <v>5</v>
       </c>
-      <c r="C33" s="149"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="151"/>
-    </row>
-    <row r="34" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="50"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="186"/>
-    </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="52"/>
-      <c r="B35" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="178" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="179"/>
-      <c r="E35" s="179"/>
-      <c r="F35" s="180"/>
-    </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="B36" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="164" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="166"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="53"/>
-      <c r="B37" s="30" t="s">
-        <v>28</v>
+      <c r="C33" s="200"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="202"/>
+      <c r="G33" s="73"/>
+    </row>
+    <row r="34" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="190"/>
+      <c r="D34" s="191"/>
+      <c r="E34" s="191"/>
+      <c r="F34" s="192"/>
+      <c r="G34" s="76"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="53"/>
+      <c r="B35" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="181" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="182"/>
+      <c r="E35" s="182"/>
+      <c r="F35" s="183"/>
+      <c r="G35" s="92" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="40"/>
+      <c r="B36" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="184" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="91" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="54"/>
+      <c r="B37" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="C37" s="169" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D37" s="170"/>
       <c r="E37" s="170"/>
       <c r="F37" s="171"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G37" s="87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="168" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E40" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C11:F11"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
@@ -3253,6 +3568,23 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3283,7 +3615,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3292,10 +3624,11 @@
     <col min="4" max="4" width="17.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3303,15 +3636,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3319,40 +3652,40 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="57"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O5" s="58"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3362,432 +3695,480 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="69" customFormat="1" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="167" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-    </row>
-    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" s="70" customFormat="1" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="193" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="75"/>
+    </row>
+    <row r="9" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="49"/>
-    </row>
-    <row r="10" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="27">
         <v>1</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="107"/>
-      <c r="E10" s="199"/>
-      <c r="F10" s="200"/>
-      <c r="G10" s="70"/>
-    </row>
-    <row r="11" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28">
+      <c r="C10" s="167" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="98"/>
+      <c r="E10" s="225"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="92" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="79"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>2</v>
       </c>
-      <c r="C11" s="164" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="166"/>
-      <c r="G11" s="70"/>
-    </row>
-    <row r="12" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="184" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="93" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="79"/>
+    </row>
+    <row r="12" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>3</v>
       </c>
-      <c r="C12" s="161" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="162"/>
-      <c r="E12" s="162"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="70"/>
-    </row>
-    <row r="13" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="197" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="198"/>
+      <c r="E12" s="198"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="91" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="79"/>
+    </row>
+    <row r="13" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>4</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="212" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="166"/>
-      <c r="G13" s="70"/>
-    </row>
-    <row r="14" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30">
+      <c r="C13" s="133"/>
+      <c r="D13" s="222"/>
+      <c r="E13" s="223" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="186"/>
+      <c r="G13" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="79"/>
+    </row>
+    <row r="14" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>5</v>
       </c>
-      <c r="C14" s="208"/>
-      <c r="D14" s="209"/>
-      <c r="E14" s="209"/>
-      <c r="F14" s="210"/>
-      <c r="G14" s="70"/>
-    </row>
-    <row r="15" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="217" t="s">
+      <c r="C14" s="219"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="220"/>
+      <c r="F14" s="221"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="79"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="230" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
+      <c r="F15" s="232"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="79"/>
+    </row>
+    <row r="16" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
+        <v>4</v>
+      </c>
+      <c r="C16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="235"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="79"/>
+    </row>
+    <row r="17" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29">
+        <v>5</v>
+      </c>
+      <c r="C17" s="152"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="154"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="79"/>
+    </row>
+    <row r="18" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="36"/>
+      <c r="B18" s="31">
+        <v>6</v>
+      </c>
+      <c r="C18" s="136"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="79"/>
+    </row>
+    <row r="19" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="33">
+        <v>1</v>
+      </c>
+      <c r="C19" s="236"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="237"/>
+      <c r="F19" s="238"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="79"/>
+    </row>
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
+        <v>2</v>
+      </c>
+      <c r="C20" s="146"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="79"/>
+    </row>
+    <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29">
+        <v>3</v>
+      </c>
+      <c r="C21" s="233" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="79"/>
+    </row>
+    <row r="22" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="36"/>
+      <c r="B22" s="31">
+        <v>4</v>
+      </c>
+      <c r="C22" s="227" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="228"/>
+      <c r="E22" s="228"/>
+      <c r="F22" s="229"/>
+      <c r="G22" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="79"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="33">
+        <v>2</v>
+      </c>
+      <c r="C23" s="181" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="182"/>
+      <c r="E23" s="182"/>
+      <c r="F23" s="183"/>
+      <c r="G23" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="79"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
+        <v>3</v>
+      </c>
+      <c r="C24" s="158" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="159"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="79"/>
+    </row>
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29">
+        <v>4</v>
+      </c>
+      <c r="C25" s="233" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="234"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="H25" s="79"/>
+    </row>
+    <row r="26" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="36"/>
+      <c r="B26" s="31">
+        <v>5</v>
+      </c>
+      <c r="C26" s="152" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="93" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="79"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="33">
+        <v>2</v>
+      </c>
+      <c r="C27" s="224"/>
+      <c r="D27" s="225"/>
+      <c r="E27" s="225"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="79"/>
+    </row>
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="29">
+        <v>3</v>
+      </c>
+      <c r="C28" s="239"/>
+      <c r="D28" s="240"/>
+      <c r="E28" s="240"/>
+      <c r="F28" s="241"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="79"/>
+    </row>
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="37"/>
+      <c r="B29" s="29">
+        <v>4</v>
+      </c>
+      <c r="C29" s="197" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="198"/>
+      <c r="E29" s="198"/>
+      <c r="F29" s="199"/>
+      <c r="G29" s="91" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="79"/>
+    </row>
+    <row r="30" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="38"/>
+      <c r="B30" s="31">
+        <v>5</v>
+      </c>
+      <c r="C30" s="242" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="243"/>
+      <c r="E30" s="243"/>
+      <c r="F30" s="244"/>
+      <c r="G30" s="87" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" s="79"/>
+    </row>
+    <row r="31" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="33">
+        <v>1</v>
+      </c>
+      <c r="C31" s="175" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="79"/>
+    </row>
+    <row r="32" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29">
+        <v>2</v>
+      </c>
+      <c r="C32" s="184" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="185"/>
+      <c r="E32" s="185"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="79"/>
+    </row>
+    <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="29">
+        <v>3</v>
+      </c>
+      <c r="C33" s="184" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="185"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="186"/>
+      <c r="G33" s="93" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="79"/>
+    </row>
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="41"/>
+      <c r="B34" s="31">
+        <v>4</v>
+      </c>
+      <c r="C34" s="200"/>
+      <c r="D34" s="201"/>
+      <c r="E34" s="201"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="79"/>
+    </row>
+    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="64"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="212"/>
+      <c r="D35" s="213"/>
+      <c r="E35" s="213"/>
+      <c r="F35" s="214"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="79"/>
+    </row>
+    <row r="36" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="54"/>
+      <c r="B36" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
-      <c r="F15" s="219"/>
-      <c r="G15" s="70"/>
-    </row>
-    <row r="16" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
-        <v>4</v>
-      </c>
-      <c r="C16" s="187"/>
-      <c r="D16" s="188"/>
-      <c r="E16" s="188"/>
-      <c r="F16" s="189"/>
-      <c r="G16" s="70"/>
-    </row>
-    <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28">
-        <v>5</v>
-      </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="70"/>
-    </row>
-    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="35"/>
-      <c r="B18" s="30">
-        <v>6</v>
-      </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="70"/>
-    </row>
-    <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32">
-        <v>1</v>
-      </c>
-      <c r="C19" s="190"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="192"/>
-      <c r="G19" s="70"/>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
-        <v>2</v>
-      </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="70"/>
-    </row>
-    <row r="21" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28">
-        <v>3</v>
-      </c>
-      <c r="C21" s="187" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="188"/>
-      <c r="E21" s="188"/>
-      <c r="F21" s="189"/>
-      <c r="G21" s="70"/>
-    </row>
-    <row r="22" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="35"/>
-      <c r="B22" s="30">
-        <v>4</v>
-      </c>
-      <c r="C22" s="214" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="215"/>
-      <c r="E22" s="215"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="70"/>
-    </row>
-    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32">
-        <v>2</v>
-      </c>
-      <c r="C23" s="178" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="179"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="180"/>
-      <c r="G23" s="70"/>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
-        <v>3</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="97"/>
-      <c r="G24" s="70"/>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28">
-        <v>4</v>
-      </c>
-      <c r="C25" s="187" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="188"/>
-      <c r="E25" s="188"/>
-      <c r="F25" s="189"/>
-      <c r="G25" s="70"/>
-    </row>
-    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="35"/>
-      <c r="B26" s="30">
-        <v>5</v>
-      </c>
-      <c r="C26" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="70"/>
-    </row>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="32">
-        <v>2</v>
-      </c>
-      <c r="C27" s="213"/>
-      <c r="D27" s="199"/>
-      <c r="E27" s="199"/>
-      <c r="F27" s="200"/>
-      <c r="G27" s="70"/>
-    </row>
-    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="28">
-        <v>3</v>
-      </c>
-      <c r="C28" s="193"/>
-      <c r="D28" s="194"/>
-      <c r="E28" s="194"/>
-      <c r="F28" s="195"/>
-      <c r="G28" s="70"/>
-    </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="36"/>
-      <c r="B29" s="28">
-        <v>4</v>
-      </c>
-      <c r="C29" s="161" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="162"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="163"/>
-      <c r="G29" s="70"/>
-    </row>
-    <row r="30" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="37"/>
-      <c r="B30" s="30">
-        <v>5</v>
-      </c>
-      <c r="C30" s="196" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30" s="197"/>
-      <c r="E30" s="197"/>
-      <c r="F30" s="198"/>
-      <c r="G30" s="70"/>
-    </row>
-    <row r="31" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="32">
-        <v>1</v>
-      </c>
-      <c r="C31" s="172" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="70"/>
-    </row>
-    <row r="32" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="28">
-        <v>2</v>
-      </c>
-      <c r="C32" s="164" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="166"/>
-      <c r="G32" s="70"/>
-    </row>
-    <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="39"/>
-      <c r="B33" s="28">
-        <v>3</v>
-      </c>
-      <c r="C33" s="164" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="165"/>
-      <c r="E33" s="165"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="70"/>
-    </row>
-    <row r="34" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="40"/>
-      <c r="B34" s="30">
-        <v>4</v>
-      </c>
-      <c r="C34" s="149"/>
-      <c r="D34" s="150"/>
-      <c r="E34" s="150"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="70"/>
-    </row>
-    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="63"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="201"/>
-      <c r="D35" s="202"/>
-      <c r="E35" s="202"/>
-      <c r="F35" s="203"/>
-      <c r="G35" s="70"/>
-    </row>
-    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="53"/>
-      <c r="B36" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="205" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="207"/>
-      <c r="G36" s="70"/>
-    </row>
-    <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="71" t="s">
+      <c r="D36" s="217"/>
+      <c r="E36" s="217"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="72"/>
-      <c r="C37" s="204" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="204"/>
-      <c r="E37" s="204"/>
-      <c r="F37" s="204"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H36" s="79"/>
+    </row>
+    <row r="37" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="82"/>
+      <c r="C37" s="215" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="215"/>
+      <c r="E37" s="215"/>
+      <c r="F37" s="215"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
@@ -3804,6 +4185,21 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3834,7 +4230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3843,10 +4239,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3854,15 +4251,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3870,39 +4267,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3912,35 +4309,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="58" t="s">
-        <v>47</v>
+      <c r="D7" s="55"/>
+      <c r="E7" s="59" t="s">
+        <v>60</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="69" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="167" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" s="70" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="193" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>0</v>
@@ -3951,326 +4348,375 @@
       <c r="D9" s="22"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="G9" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="27">
         <v>2</v>
       </c>
-      <c r="C10" s="235"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="237"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28">
+      <c r="C10" s="251"/>
+      <c r="D10" s="252"/>
+      <c r="E10" s="252"/>
+      <c r="F10" s="253"/>
+      <c r="G10" s="71"/>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29">
         <v>3</v>
       </c>
-      <c r="C11" s="164" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="166"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28">
+      <c r="C11" s="184" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>4</v>
       </c>
-      <c r="C12" s="164" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="166"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30">
+      <c r="C12" s="184" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31">
         <v>5</v>
       </c>
-      <c r="C13" s="238"/>
-      <c r="D13" s="239"/>
-      <c r="E13" s="239"/>
-      <c r="F13" s="240"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="32">
+      <c r="C13" s="254"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
+      <c r="F13" s="256"/>
+      <c r="G13" s="73"/>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="33">
         <v>2</v>
       </c>
-      <c r="C14" s="232"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="234"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="248"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29">
         <v>3</v>
       </c>
-      <c r="C15" s="164" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-      <c r="F15" s="166"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28">
+      <c r="C15" s="184" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
+      <c r="F15" s="186"/>
+      <c r="G15" s="93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29">
         <v>4</v>
       </c>
-      <c r="C16" s="89" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="91"/>
-    </row>
-    <row r="17" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="35"/>
-      <c r="B17" s="30">
+      <c r="C16" s="152" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="36"/>
+      <c r="B17" s="31">
         <v>5</v>
       </c>
-      <c r="C17" s="229" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="231"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="32">
+      <c r="C17" s="266" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="267"/>
+      <c r="E17" s="267"/>
+      <c r="F17" s="268"/>
+      <c r="G17" s="93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="33">
         <v>2</v>
       </c>
-      <c r="C18" s="241"/>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="243"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28">
+      <c r="C18" s="245"/>
+      <c r="D18" s="246"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="247"/>
+      <c r="G18" s="89"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29">
         <v>3</v>
       </c>
-      <c r="C19" s="193"/>
-      <c r="D19" s="194"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="195"/>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28">
+      <c r="C19" s="239"/>
+      <c r="D19" s="240"/>
+      <c r="E19" s="240"/>
+      <c r="F19" s="241"/>
+      <c r="G19" s="88"/>
+    </row>
+    <row r="20" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29">
         <v>4</v>
       </c>
-      <c r="C20" s="161" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="163"/>
-    </row>
-    <row r="21" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="35"/>
-      <c r="B21" s="30">
+      <c r="C20" s="197" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="198"/>
+      <c r="E20" s="198"/>
+      <c r="F20" s="199"/>
+      <c r="G20" s="91" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="36"/>
+      <c r="B21" s="31">
         <v>5</v>
       </c>
-      <c r="C21" s="152"/>
-      <c r="D21" s="153"/>
-      <c r="E21" s="153" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="154"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="C21" s="203"/>
+      <c r="D21" s="204"/>
+      <c r="E21" s="204" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="205"/>
+      <c r="G21" s="90" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="33">
         <v>1</v>
       </c>
-      <c r="C22" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="174"/>
-    </row>
-    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28">
+      <c r="C22" s="175" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29">
         <v>2</v>
       </c>
-      <c r="C23" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="91"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28">
+      <c r="C23" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="154"/>
+      <c r="G23" s="93" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29">
         <v>3</v>
       </c>
-      <c r="C24" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="91"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="35"/>
-      <c r="B25" s="30">
+      <c r="C24" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="93" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="36"/>
+      <c r="B25" s="31">
         <v>4</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="151"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32">
+      <c r="C25" s="200"/>
+      <c r="D25" s="201"/>
+      <c r="E25" s="201"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="73"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="33">
         <v>4</v>
       </c>
-      <c r="C26" s="223" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="224"/>
-      <c r="E26" s="224"/>
-      <c r="F26" s="225"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="66"/>
-      <c r="B27" s="28">
+      <c r="C26" s="260" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="261"/>
+      <c r="E26" s="261"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="95" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="67"/>
+      <c r="B27" s="29">
         <v>5</v>
       </c>
-      <c r="C27" s="164" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-      <c r="F27" s="166"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="66"/>
-      <c r="B28" s="28">
+      <c r="C27" s="184" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="186"/>
+      <c r="G27" s="93" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="67"/>
+      <c r="B28" s="29">
         <v>6</v>
       </c>
-      <c r="C28" s="164" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="165"/>
-      <c r="E28" s="165"/>
-      <c r="F28" s="166"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="67"/>
-      <c r="B29" s="30">
+      <c r="C28" s="184" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="185"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="186"/>
+      <c r="G28" s="93" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="68"/>
+      <c r="B29" s="31">
         <v>7</v>
       </c>
-      <c r="C29" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="110"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="26">
+      <c r="C29" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="27">
         <v>2</v>
       </c>
-      <c r="C30" s="226"/>
-      <c r="D30" s="227"/>
-      <c r="E30" s="227"/>
-      <c r="F30" s="228"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="39"/>
-      <c r="B31" s="28">
+      <c r="C30" s="263"/>
+      <c r="D30" s="264"/>
+      <c r="E30" s="264"/>
+      <c r="F30" s="265"/>
+      <c r="G30" s="96"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="40"/>
+      <c r="B31" s="29">
         <v>3</v>
       </c>
-      <c r="C31" s="220" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="221"/>
-      <c r="E31" s="221"/>
-      <c r="F31" s="222"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="39"/>
-      <c r="B32" s="28">
+      <c r="C31" s="257" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="258"/>
+      <c r="E31" s="258"/>
+      <c r="F31" s="259"/>
+      <c r="G31" s="93" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="29">
         <v>4</v>
       </c>
-      <c r="C32" s="220" t="s">
-        <v>103</v>
-      </c>
-      <c r="D32" s="221"/>
-      <c r="E32" s="221"/>
-      <c r="F32" s="222"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="53"/>
-      <c r="B33" s="30">
+      <c r="C32" s="257" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="258"/>
+      <c r="E32" s="258"/>
+      <c r="F32" s="259"/>
+      <c r="G32" s="93" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="54"/>
+      <c r="B33" s="31">
         <v>5</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="126"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="136"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="73"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
@@ -4287,6 +4733,17 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
